--- a/Mataquito/supplemental/Table_S8.xlsx
+++ b/Mataquito/supplemental/Table_S8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Glong1/Desktop/Andes/Chapter_1_Manuscript/MataquitoWatershedAnalysis/Mataquito/supplemental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B9E1FB-FC0A-4141-BFF6-62F85D351B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7837C5-8D9B-4846-8B32-B5B0F9C13917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -121,8 +121,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,8 +432,8 @@
     <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -456,10 +457,10 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -479,10 +480,10 @@
       <c r="E3">
         <v>52</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>7.4660000000000002E-6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>7.3E-7</v>
       </c>
     </row>
@@ -502,10 +503,10 @@
       <c r="E4">
         <v>32</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>5.9050000000000002E-6</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>4.8999999999999997E-7</v>
       </c>
     </row>
@@ -525,10 +526,10 @@
       <c r="E5">
         <v>1.86</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>3.8669999999999999E-7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>3.1E-8</v>
       </c>
     </row>
@@ -548,10 +549,10 @@
       <c r="E6">
         <v>2.44</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>4.6590000000000001E-7</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>3.8000000000000003E-8</v>
       </c>
     </row>
